--- a/vendor_map_lowes.xlsx
+++ b/vendor_map_lowes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\svr01\home\gfetzer\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\svr01\home\gfetzer\Desktop\Chat GPT Automation\Order Splitter\Vendor Maps\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34DA6D7B-FDCC-4C64-9568-5D48DBA2AE40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5755CD7-D0CC-4AEB-AA3B-42470BA4D7CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="77040" windowHeight="21390" xr2:uid="{2C04AEF6-1DD2-46BE-907B-9745C127F2C9}"/>
+    <workbookView xWindow="76680" yWindow="-825" windowWidth="29040" windowHeight="15990" xr2:uid="{2C04AEF6-1DD2-46BE-907B-9745C127F2C9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="85">
   <si>
     <t>SKU</t>
   </si>
@@ -217,12 +217,6 @@
   </si>
   <si>
     <t>PenaShield</t>
-  </si>
-  <si>
-    <t>SuperDuper 8 oz</t>
-  </si>
-  <si>
-    <t>SuperDuper 140 oz</t>
   </si>
   <si>
     <t>UP-CLEANER-XTRA</t>
@@ -650,7 +644,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D34B957F-2E4F-4F5D-9C8E-E382ADBC502B}">
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
@@ -665,7 +659,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D1" t="s">
         <v>49</v>
@@ -949,10 +943,10 @@
         <v>54</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C26" t="s">
         <v>84</v>
-      </c>
-      <c r="C26" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -960,10 +954,10 @@
         <v>54</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C27" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -985,7 +979,7 @@
         <v>6102</v>
       </c>
       <c r="C29" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -996,7 +990,7 @@
         <v>20</v>
       </c>
       <c r="C30" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -1007,7 +1001,7 @@
         <v>21</v>
       </c>
       <c r="C31" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -1018,7 +1012,7 @@
         <v>22</v>
       </c>
       <c r="C32" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -1029,7 +1023,7 @@
         <v>23</v>
       </c>
       <c r="C33" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -1040,7 +1034,7 @@
         <v>24</v>
       </c>
       <c r="C34" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -1051,7 +1045,7 @@
         <v>25</v>
       </c>
       <c r="C35" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -1125,7 +1119,7 @@
         <v>54</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C42" t="s">
         <v>45</v>
@@ -1158,10 +1152,10 @@
         <v>54</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C45" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -1191,7 +1185,7 @@
         <v>54</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C48" t="s">
         <v>47</v>
@@ -1235,7 +1229,7 @@
         <v>54</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C52" t="s">
         <v>47</v>
@@ -1246,7 +1240,7 @@
         <v>54</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C53" t="s">
         <v>47</v>
@@ -1278,33 +1272,33 @@
       <c r="A56" t="s">
         <v>54</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>64</v>
+      <c r="B56" s="2">
+        <v>123118</v>
       </c>
       <c r="C56" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>54</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>65</v>
+      <c r="B57" s="2">
+        <v>123119</v>
       </c>
       <c r="C57" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>54</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>33</v>
+      <c r="B58" s="2">
+        <v>123124</v>
       </c>
       <c r="C58" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -1312,10 +1306,10 @@
         <v>54</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C59" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -1323,10 +1317,10 @@
         <v>54</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C60" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -1334,10 +1328,10 @@
         <v>54</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C61" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -1345,10 +1339,10 @@
         <v>54</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C62" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -1356,10 +1350,10 @@
         <v>54</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C63" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -1367,10 +1361,10 @@
         <v>54</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C64" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -1378,10 +1372,10 @@
         <v>54</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C65" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -1389,10 +1383,10 @@
         <v>54</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C66" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -1400,10 +1394,10 @@
         <v>54</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="C67" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -1411,10 +1405,10 @@
         <v>54</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C68" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -1422,10 +1416,10 @@
         <v>54</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C69" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -1433,10 +1427,10 @@
         <v>54</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C70" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -1444,10 +1438,10 @@
         <v>54</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C71" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -1455,10 +1449,10 @@
         <v>54</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C72" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
@@ -1466,10 +1460,21 @@
         <v>54</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C73" t="s">
-        <v>75</v>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>54</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C74" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/vendor_map_lowes.xlsx
+++ b/vendor_map_lowes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\svr01\home\gfetzer\Desktop\Chat GPT Automation\Order Splitter\Vendor Maps\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\svr01\home\gfetzer\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5755CD7-D0CC-4AEB-AA3B-42470BA4D7CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34DA6D7B-FDCC-4C64-9568-5D48DBA2AE40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="76680" yWindow="-825" windowWidth="29040" windowHeight="15990" xr2:uid="{2C04AEF6-1DD2-46BE-907B-9745C127F2C9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="77040" windowHeight="21390" xr2:uid="{2C04AEF6-1DD2-46BE-907B-9745C127F2C9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="87">
   <si>
     <t>SKU</t>
   </si>
@@ -217,6 +217,12 @@
   </si>
   <si>
     <t>PenaShield</t>
+  </si>
+  <si>
+    <t>SuperDuper 8 oz</t>
+  </si>
+  <si>
+    <t>SuperDuper 140 oz</t>
   </si>
   <si>
     <t>UP-CLEANER-XTRA</t>
@@ -644,7 +650,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D34B957F-2E4F-4F5D-9C8E-E382ADBC502B}">
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
@@ -659,7 +665,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D1" t="s">
         <v>49</v>
@@ -943,10 +949,10 @@
         <v>54</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C26" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -954,10 +960,10 @@
         <v>54</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C27" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -979,7 +985,7 @@
         <v>6102</v>
       </c>
       <c r="C29" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -990,7 +996,7 @@
         <v>20</v>
       </c>
       <c r="C30" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -1001,7 +1007,7 @@
         <v>21</v>
       </c>
       <c r="C31" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -1012,7 +1018,7 @@
         <v>22</v>
       </c>
       <c r="C32" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -1023,7 +1029,7 @@
         <v>23</v>
       </c>
       <c r="C33" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -1034,7 +1040,7 @@
         <v>24</v>
       </c>
       <c r="C34" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -1045,7 +1051,7 @@
         <v>25</v>
       </c>
       <c r="C35" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -1119,7 +1125,7 @@
         <v>54</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C42" t="s">
         <v>45</v>
@@ -1152,10 +1158,10 @@
         <v>54</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C45" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -1185,7 +1191,7 @@
         <v>54</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C48" t="s">
         <v>47</v>
@@ -1229,7 +1235,7 @@
         <v>54</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C52" t="s">
         <v>47</v>
@@ -1240,7 +1246,7 @@
         <v>54</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C53" t="s">
         <v>47</v>
@@ -1272,33 +1278,33 @@
       <c r="A56" t="s">
         <v>54</v>
       </c>
-      <c r="B56" s="2">
-        <v>123118</v>
+      <c r="B56" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="C56" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>54</v>
       </c>
-      <c r="B57" s="2">
-        <v>123119</v>
+      <c r="B57" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="C57" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>54</v>
       </c>
-      <c r="B58" s="2">
-        <v>123124</v>
+      <c r="B58" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="C58" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -1306,10 +1312,10 @@
         <v>54</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C59" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -1317,10 +1323,10 @@
         <v>54</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C60" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -1328,10 +1334,10 @@
         <v>54</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C61" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -1339,10 +1345,10 @@
         <v>54</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C62" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -1350,10 +1356,10 @@
         <v>54</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C63" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -1361,10 +1367,10 @@
         <v>54</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C64" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -1372,10 +1378,10 @@
         <v>54</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C65" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -1383,10 +1389,10 @@
         <v>54</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C66" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -1394,10 +1400,10 @@
         <v>54</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="C67" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -1405,10 +1411,10 @@
         <v>54</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C68" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -1416,10 +1422,10 @@
         <v>54</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C69" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -1427,10 +1433,10 @@
         <v>54</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C70" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -1438,10 +1444,10 @@
         <v>54</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C71" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -1449,10 +1455,10 @@
         <v>54</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C72" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
@@ -1460,21 +1466,10 @@
         <v>54</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C73" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>54</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C74" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/vendor_map_lowes.xlsx
+++ b/vendor_map_lowes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\svr01\home\gfetzer\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\svr01\home\gfetzer\Desktop\Chat GPT Automation\Order Splitter\Vendor Maps\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34DA6D7B-FDCC-4C64-9568-5D48DBA2AE40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FF05A87-6563-430C-8A4E-F77764A9F31A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="77040" windowHeight="21390" xr2:uid="{2C04AEF6-1DD2-46BE-907B-9745C127F2C9}"/>
+    <workbookView xWindow="38400" yWindow="0" windowWidth="38400" windowHeight="21150" xr2:uid="{2C04AEF6-1DD2-46BE-907B-9745C127F2C9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="85">
   <si>
     <t>SKU</t>
   </si>
@@ -219,12 +219,6 @@
     <t>PenaShield</t>
   </si>
   <si>
-    <t>SuperDuper 8 oz</t>
-  </si>
-  <si>
-    <t>SuperDuper 140 oz</t>
-  </si>
-  <si>
     <t>UP-CLEANER-XTRA</t>
   </si>
   <si>
@@ -267,9 +261,6 @@
     <t>PPS24KIT</t>
   </si>
   <si>
-    <t>6660C6LN</t>
-  </si>
-  <si>
     <t>Home Selects</t>
   </si>
   <si>
@@ -286,6 +277,9 @@
   </si>
   <si>
     <t>Gate Latch</t>
+  </si>
+  <si>
+    <t>6660CLN</t>
   </si>
 </sst>
 </file>
@@ -650,7 +644,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D34B957F-2E4F-4F5D-9C8E-E382ADBC502B}">
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
@@ -665,7 +659,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D1" t="s">
         <v>49</v>
@@ -949,10 +943,10 @@
         <v>54</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C26" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -960,10 +954,10 @@
         <v>54</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C27" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -985,7 +979,7 @@
         <v>6102</v>
       </c>
       <c r="C29" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -996,7 +990,7 @@
         <v>20</v>
       </c>
       <c r="C30" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -1007,7 +1001,7 @@
         <v>21</v>
       </c>
       <c r="C31" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -1018,7 +1012,7 @@
         <v>22</v>
       </c>
       <c r="C32" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -1029,7 +1023,7 @@
         <v>23</v>
       </c>
       <c r="C33" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -1040,7 +1034,7 @@
         <v>24</v>
       </c>
       <c r="C34" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -1051,7 +1045,7 @@
         <v>25</v>
       </c>
       <c r="C35" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -1125,7 +1119,7 @@
         <v>54</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C42" t="s">
         <v>45</v>
@@ -1158,10 +1152,10 @@
         <v>54</v>
       </c>
       <c r="B45" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C45" t="s">
         <v>79</v>
-      </c>
-      <c r="C45" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -1191,7 +1185,7 @@
         <v>54</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C48" t="s">
         <v>47</v>
@@ -1235,7 +1229,7 @@
         <v>54</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C52" t="s">
         <v>47</v>
@@ -1246,7 +1240,7 @@
         <v>54</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C53" t="s">
         <v>47</v>
@@ -1278,33 +1272,33 @@
       <c r="A56" t="s">
         <v>54</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>64</v>
+      <c r="B56" s="2">
+        <v>123118</v>
       </c>
       <c r="C56" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>54</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>65</v>
+      <c r="B57" s="2">
+        <v>123119</v>
       </c>
       <c r="C57" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>54</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>33</v>
+      <c r="B58" s="2">
+        <v>123124</v>
       </c>
       <c r="C58" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -1312,10 +1306,10 @@
         <v>54</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C59" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -1323,10 +1317,10 @@
         <v>54</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C60" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -1334,10 +1328,10 @@
         <v>54</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C61" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -1345,10 +1339,10 @@
         <v>54</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C62" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -1356,10 +1350,10 @@
         <v>54</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C63" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -1367,10 +1361,10 @@
         <v>54</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C64" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -1378,10 +1372,10 @@
         <v>54</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C65" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -1389,10 +1383,10 @@
         <v>54</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C66" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -1400,10 +1394,10 @@
         <v>54</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="C67" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -1411,10 +1405,10 @@
         <v>54</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C68" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -1422,10 +1416,10 @@
         <v>54</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C69" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -1433,10 +1427,10 @@
         <v>54</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C70" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -1444,10 +1438,10 @@
         <v>54</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C71" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -1455,10 +1449,10 @@
         <v>54</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C72" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
@@ -1466,10 +1460,21 @@
         <v>54</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C73" t="s">
-        <v>75</v>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>54</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C74" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/vendor_map_lowes.xlsx
+++ b/vendor_map_lowes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\svr01\home\gfetzer\Desktop\Chat GPT Automation\Order Splitter\Vendor Maps\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\svr01\home\gfetzer\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FF05A87-6563-430C-8A4E-F77764A9F31A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34DA6D7B-FDCC-4C64-9568-5D48DBA2AE40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38400" yWindow="0" windowWidth="38400" windowHeight="21150" xr2:uid="{2C04AEF6-1DD2-46BE-907B-9745C127F2C9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="77040" windowHeight="21390" xr2:uid="{2C04AEF6-1DD2-46BE-907B-9745C127F2C9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="87">
   <si>
     <t>SKU</t>
   </si>
@@ -219,6 +219,12 @@
     <t>PenaShield</t>
   </si>
   <si>
+    <t>SuperDuper 8 oz</t>
+  </si>
+  <si>
+    <t>SuperDuper 140 oz</t>
+  </si>
+  <si>
     <t>UP-CLEANER-XTRA</t>
   </si>
   <si>
@@ -261,6 +267,9 @@
     <t>PPS24KIT</t>
   </si>
   <si>
+    <t>6660C6LN</t>
+  </si>
+  <si>
     <t>Home Selects</t>
   </si>
   <si>
@@ -277,9 +286,6 @@
   </si>
   <si>
     <t>Gate Latch</t>
-  </si>
-  <si>
-    <t>6660CLN</t>
   </si>
 </sst>
 </file>
@@ -644,7 +650,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D34B957F-2E4F-4F5D-9C8E-E382ADBC502B}">
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
@@ -659,7 +665,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D1" t="s">
         <v>49</v>
@@ -943,10 +949,10 @@
         <v>54</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C26" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -954,10 +960,10 @@
         <v>54</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C27" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -979,7 +985,7 @@
         <v>6102</v>
       </c>
       <c r="C29" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -990,7 +996,7 @@
         <v>20</v>
       </c>
       <c r="C30" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -1001,7 +1007,7 @@
         <v>21</v>
       </c>
       <c r="C31" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -1012,7 +1018,7 @@
         <v>22</v>
       </c>
       <c r="C32" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -1023,7 +1029,7 @@
         <v>23</v>
       </c>
       <c r="C33" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -1034,7 +1040,7 @@
         <v>24</v>
       </c>
       <c r="C34" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -1045,7 +1051,7 @@
         <v>25</v>
       </c>
       <c r="C35" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -1119,7 +1125,7 @@
         <v>54</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C42" t="s">
         <v>45</v>
@@ -1152,10 +1158,10 @@
         <v>54</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C45" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -1185,7 +1191,7 @@
         <v>54</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C48" t="s">
         <v>47</v>
@@ -1229,7 +1235,7 @@
         <v>54</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C52" t="s">
         <v>47</v>
@@ -1240,7 +1246,7 @@
         <v>54</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C53" t="s">
         <v>47</v>
@@ -1272,33 +1278,33 @@
       <c r="A56" t="s">
         <v>54</v>
       </c>
-      <c r="B56" s="2">
-        <v>123118</v>
+      <c r="B56" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="C56" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>54</v>
       </c>
-      <c r="B57" s="2">
-        <v>123119</v>
+      <c r="B57" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="C57" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>54</v>
       </c>
-      <c r="B58" s="2">
-        <v>123124</v>
+      <c r="B58" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="C58" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -1306,10 +1312,10 @@
         <v>54</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C59" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -1317,10 +1323,10 @@
         <v>54</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C60" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -1328,10 +1334,10 @@
         <v>54</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C61" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -1339,10 +1345,10 @@
         <v>54</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C62" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -1350,10 +1356,10 @@
         <v>54</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C63" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -1361,10 +1367,10 @@
         <v>54</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C64" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -1372,10 +1378,10 @@
         <v>54</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C65" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -1383,10 +1389,10 @@
         <v>54</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C66" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -1394,10 +1400,10 @@
         <v>54</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="C67" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -1405,10 +1411,10 @@
         <v>54</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C68" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -1416,10 +1422,10 @@
         <v>54</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C69" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -1427,10 +1433,10 @@
         <v>54</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C70" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -1438,10 +1444,10 @@
         <v>54</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C71" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -1449,10 +1455,10 @@
         <v>54</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C72" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
@@ -1460,21 +1466,10 @@
         <v>54</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C73" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>54</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C74" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/vendor_map_lowes.xlsx
+++ b/vendor_map_lowes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\svr01\home\gfetzer\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\svr01\home\gfetzer\Desktop\Chat GPT Automation\Order Splitter\v1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34DA6D7B-FDCC-4C64-9568-5D48DBA2AE40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{542F6BF0-AFA8-4265-B97C-D6E0C5C09F8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="77040" windowHeight="21390" xr2:uid="{2C04AEF6-1DD2-46BE-907B-9745C127F2C9}"/>
+    <workbookView xWindow="13695" yWindow="5535" windowWidth="21600" windowHeight="15555" xr2:uid="{2C04AEF6-1DD2-46BE-907B-9745C127F2C9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -267,9 +267,6 @@
     <t>PPS24KIT</t>
   </si>
   <si>
-    <t>6660C6LN</t>
-  </si>
-  <si>
     <t>Home Selects</t>
   </si>
   <si>
@@ -286,6 +283,9 @@
   </si>
   <si>
     <t>Gate Latch</t>
+  </si>
+  <si>
+    <t>6660CLN</t>
   </si>
 </sst>
 </file>
@@ -665,7 +665,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D1" t="s">
         <v>49</v>
@@ -949,10 +949,10 @@
         <v>54</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C26" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -960,10 +960,10 @@
         <v>54</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C27" t="s">
         <v>85</v>
-      </c>
-      <c r="C27" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -985,7 +985,7 @@
         <v>6102</v>
       </c>
       <c r="C29" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -996,7 +996,7 @@
         <v>20</v>
       </c>
       <c r="C30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -1007,7 +1007,7 @@
         <v>21</v>
       </c>
       <c r="C31" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -1018,7 +1018,7 @@
         <v>22</v>
       </c>
       <c r="C32" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -1029,7 +1029,7 @@
         <v>23</v>
       </c>
       <c r="C33" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -1040,7 +1040,7 @@
         <v>24</v>
       </c>
       <c r="C34" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -1051,7 +1051,7 @@
         <v>25</v>
       </c>
       <c r="C35" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -1161,7 +1161,7 @@
         <v>79</v>
       </c>
       <c r="C45" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -1246,7 +1246,7 @@
         <v>54</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C53" t="s">
         <v>47</v>
